--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.44917744904917</v>
+        <v>9.822991335470491</v>
       </c>
       <c r="D2" t="n">
-        <v>25.17997440648243</v>
+        <v>4.091745841053395</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F2" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.1180858081365</v>
+        <v>10.74418894382218</v>
       </c>
       <c r="D3" t="n">
-        <v>19.32567008758689</v>
+        <v>3.14042138923287</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F3" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.99125964462448</v>
+        <v>13.16107969225148</v>
       </c>
       <c r="D4" t="n">
-        <v>37.18298429372841</v>
+        <v>6.042234947730867</v>
       </c>
       <c r="E4" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F4" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.29172639330862</v>
+        <v>8.497405538912652</v>
       </c>
       <c r="D5" t="n">
-        <v>18.86054081939328</v>
+        <v>3.064837883151407</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F5" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.40636534723889</v>
+        <v>10.79103436892632</v>
       </c>
       <c r="D6" t="n">
-        <v>25.03437636531016</v>
+        <v>4.068086159362901</v>
       </c>
       <c r="E6" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F6" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.71030004162068</v>
+        <v>8.240423756763361</v>
       </c>
       <c r="D7" t="n">
-        <v>7.410802925459561</v>
+        <v>1.204255475387179</v>
       </c>
       <c r="E7" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F7" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.57907479323426</v>
+        <v>5.619099653900567</v>
       </c>
       <c r="D8" t="n">
-        <v>45.11938746307309</v>
+        <v>7.331900462749378</v>
       </c>
       <c r="E8" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F8" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.16295090390226</v>
+        <v>4.251479521884117</v>
       </c>
       <c r="D9" t="n">
-        <v>28.26550344272776</v>
+        <v>4.593144309443261</v>
       </c>
       <c r="E9" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F9" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.44468116466937</v>
+        <v>4.134760689258772</v>
       </c>
       <c r="D10" t="n">
-        <v>11.10825261453616</v>
+        <v>1.805091049862126</v>
       </c>
       <c r="E10" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F10" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.24601890638081</v>
+        <v>6.377478072286882</v>
       </c>
       <c r="D11" t="n">
-        <v>11.74230945292708</v>
+        <v>1.90812528610065</v>
       </c>
       <c r="E11" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F11" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.21014774728082</v>
+        <v>2.959149008933134</v>
       </c>
       <c r="D12" t="n">
-        <v>20.86242387582906</v>
+        <v>3.390143879822222</v>
       </c>
       <c r="E12" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F12" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.896053046305965</v>
+        <v>0.7956086200247194</v>
       </c>
       <c r="D13" t="n">
-        <v>3.33259267275831</v>
+        <v>0.5415463093232254</v>
       </c>
       <c r="E13" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F13" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.45291802108919</v>
+        <v>3.323599178426993</v>
       </c>
       <c r="D14" t="n">
-        <v>11.14296858323708</v>
+        <v>1.810732394776025</v>
       </c>
       <c r="E14" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F14" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.36904669708163</v>
+        <v>3.147470088275766</v>
       </c>
       <c r="D15" t="n">
-        <v>9.247723270475381</v>
+        <v>1.50275503145225</v>
       </c>
       <c r="E15" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F15" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.64140547904983</v>
+        <v>6.604228390345598</v>
       </c>
       <c r="D16" t="n">
-        <v>51.59304344944553</v>
+        <v>8.383869560534899</v>
       </c>
       <c r="E16" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F16" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7.97558775263617</v>
+        <v>1.296033009803378</v>
       </c>
       <c r="D17" t="n">
-        <v>7.815820970513471</v>
+        <v>1.270070907708439</v>
       </c>
       <c r="E17" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F17" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.06185038204827</v>
+        <v>4.885050687082844</v>
       </c>
       <c r="D18" t="n">
-        <v>54.41581456812458</v>
+        <v>8.842569867320245</v>
       </c>
       <c r="E18" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F18" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.16780922476357</v>
+        <v>4.41476899902408</v>
       </c>
       <c r="D19" t="n">
-        <v>43.09921770010526</v>
+        <v>7.003622876267104</v>
       </c>
       <c r="E19" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F19" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>37.4508456621253</v>
+        <v>6.085762420095361</v>
       </c>
       <c r="D20" t="n">
-        <v>47.39430507513057</v>
+        <v>7.701574574708719</v>
       </c>
       <c r="E20" t="n">
-        <v>20.3247013794379</v>
+        <v>3.302763974158659</v>
       </c>
       <c r="F20" t="n">
-        <v>16.11639120692931</v>
+        <v>2.618913571126013</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
